--- a/StudentData/Tutorials/Unit4/4.2.4/monthly_expenses_comparison.xlsx
+++ b/StudentData/Tutorials/Unit4/4.2.4/monthly_expenses_comparison.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tutorials\Unit 3\Tutorial 3.3.10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.estremera\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{8644B78A-5F96-4F60-9E99-4D6AC13B492A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{515045CF-695C-4CBF-AF1A-9AE5C8C88774}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2DA4FB-F30F-4D70-AF87-7DC7D12F028B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="monthly_expenses" sheetId="2" r:id="rId1"/>
+    <sheet name="simulted data -DO NOT USE" sheetId="1" r:id="rId1"/>
+    <sheet name="monthly_expenses" sheetId="2" r:id="rId2"/>
+    <sheet name="solution" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="6">
   <si>
     <t>Department</t>
   </si>
@@ -49,12 +51,18 @@
   <si>
     <t>Development</t>
   </si>
+  <si>
+    <t>Marketing_Monthly_Expenses</t>
+  </si>
+  <si>
+    <t>Development_Monthly_Expenses</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,15 +438,1237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>2149.01424590337</v>
+      </c>
+      <c r="C2">
+        <f>ROUND(B2,2)</f>
+        <v>2149.0100000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1958.5207096486449</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C66" si="0">ROUND(B3,2)</f>
+        <v>1958.52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2194.3065614302081</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>2194.31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2456.908956922407</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>2456.91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>1929.7539875829989</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>1929.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>1929.7589129152459</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1929.76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>2473.7638446522169</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>2473.7600000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>2230.2304187458731</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>2230.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1859.1576842195141</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>1859.16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>2162.768013075789</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>2162.77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>1860.974692156261</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>1860.97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>1860.281073928923</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1860.28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>2072.5886814698101</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>2072.59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>1426.015926602661</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1426.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>1482.52465024609</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>1482.52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>1831.3137412277081</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>1831.31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>1696.150663899673</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>1696.15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>2094.274199778582</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>2094.27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>1727.592777343637</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>1727.59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>1576.3088895994131</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>1576.31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>2439.6946306764662</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>2439.69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>1932.2671098540391</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>1932.27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>2020.2584614063769</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>2020.26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>1572.5755441359629</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>1572.58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>1836.6851826424449</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>1836.69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>2033.27677691296</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>2033.28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>1654.701926773309</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>1654.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>2112.709405503701</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>2112.71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>1819.808393024359</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>1819.81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>1912.491875062017</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>1912.49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32">
+        <v>1819.4880163311809</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>1819.49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33">
+        <v>2555.683455352681</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>2555.6799999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34">
+        <v>1995.9508325786201</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>1995.95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35">
+        <v>1682.68672131323</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>1682.69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36">
+        <v>2246.763473630956</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>2246.7600000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37">
+        <v>1633.7469050086929</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>1633.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38">
+        <v>2062.6590785014268</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>2062.66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39">
+        <v>1412.0989628360669</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>1412.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40">
+        <v>1601.544185330471</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="0"/>
+        <v>1601.54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41">
+        <v>2059.058370760737</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>2059.06</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42">
+        <v>2221.5399739986228</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>2221.54</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43">
+        <v>2051.4104843569912</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>2051.41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>1965.3055152835279</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>1965.31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45">
+        <v>1909.6688913232131</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="0"/>
+        <v>1909.67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B46">
+        <v>1556.443402889772</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>1556.44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B47">
+        <v>1784.0467374815869</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="0"/>
+        <v>1784.05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48">
+        <v>1861.8083687120641</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>1861.81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>2</v>
+      </c>
+      <c r="B49">
+        <v>2317.136667865675</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="0"/>
+        <v>2317.14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50">
+        <v>2103.0854868705378</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="0"/>
+        <v>2103.09</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51">
+        <v>1471.08795339118</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="0"/>
+        <v>1471.09</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52">
+        <v>2297.225190818438</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="0"/>
+        <v>2297.23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53">
+        <v>2084.475315875105</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="0"/>
+        <v>2084.48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54">
+        <v>1996.9233999082121</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="0"/>
+        <v>1996.92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55">
+        <v>2383.5028866522598</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="0"/>
+        <v>2383.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56">
+        <v>2509.2998567487848</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="0"/>
+        <v>2509.3000000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57">
+        <v>2479.384035734859</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="0"/>
+        <v>2479.38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58">
+        <v>1948.2347430332079</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="0"/>
+        <v>1948.23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59">
+        <v>2107.2362872446361</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="0"/>
+        <v>2107.2399999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60">
+        <v>2299.3790294210689</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="0"/>
+        <v>2299.38</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61">
+        <v>2492.6635381367082</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="0"/>
+        <v>2492.66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62">
+        <v>2056.2477286464132</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="0"/>
+        <v>2056.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63">
+        <v>2144.3023070008549</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="0"/>
+        <v>2144.3000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64">
+        <v>1868.099507798192</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="0"/>
+        <v>1868.1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65">
+        <v>1841.1380127757991</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="0"/>
+        <v>1841.14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66">
+        <v>2443.75774671826</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="0"/>
+        <v>2443.7600000000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67">
+        <v>2606.8720085712471</v>
+      </c>
+      <c r="C67">
+        <f t="shared" ref="C67:C101" si="1">ROUND(B67,2)</f>
+        <v>2606.87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68">
+        <v>2178.3969635259</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="1"/>
+        <v>2178.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69">
+        <v>2501.059869367607</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="1"/>
+        <v>2501.06</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70">
+        <v>2308.4908075142898</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="1"/>
+        <v>2308.4899999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71">
+        <v>2006.4640736184631</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="1"/>
+        <v>2006.46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72">
+        <v>2308.4186816525239</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="1"/>
+        <v>2308.42</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73">
+        <v>2661.4109699397909</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="1"/>
+        <v>2661.41</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74">
+        <v>2189.2521882670139</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="1"/>
+        <v>2189.25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75">
+        <v>2669.393096744202</v>
+      </c>
+      <c r="C75">
+        <f t="shared" si="1"/>
+        <v>2669.39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76">
+        <v>1414.0764687730771</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="1"/>
+        <v>1414.08</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77">
+        <v>2446.5707513125672</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="1"/>
+        <v>2446.5700000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78">
+        <v>2226.1141204714509</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="1"/>
+        <v>2226.11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79">
+        <v>2110.2977948602402</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="1"/>
+        <v>2110.3000000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80">
+        <v>2227.5282329606512</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="1"/>
+        <v>2227.5300000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81">
+        <v>1603.729325619732</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="1"/>
+        <v>1603.73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82">
+        <v>2134.0984336487459</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="1"/>
+        <v>2134.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83">
+        <v>2307.1337714535239</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="1"/>
+        <v>2307.13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84">
+        <v>2643.368213422455</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="1"/>
+        <v>2643.37</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85">
+        <v>2044.518934517906</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="1"/>
+        <v>2044.52</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86">
+        <v>1957.4519191320439</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="1"/>
+        <v>1957.45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87">
+        <v>2049.4728869246392</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="1"/>
+        <v>2049.4699999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88">
+        <v>2474.6206353106222</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="1"/>
+        <v>2474.62</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89">
+        <v>2298.625332897906</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="1"/>
+        <v>2298.63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90">
+        <v>2041.0719388698881</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="1"/>
+        <v>2041.07</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91">
+        <v>2353.9802299340072</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="1"/>
+        <v>2353.98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92">
+        <v>2229.123264804412</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="1"/>
+        <v>2229.12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93">
+        <v>2490.5934971598672</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="1"/>
+        <v>2490.59</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94">
+        <v>1989.384071836794</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="1"/>
+        <v>1989.38</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95">
+        <v>2101.7013560206701</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="1"/>
+        <v>2101.6999999999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96">
+        <v>2082.3675540603531</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="1"/>
+        <v>2082.37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97">
+        <v>1760.9455155603639</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="1"/>
+        <v>1760.95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98">
+        <v>2288.8360831193731</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="1"/>
+        <v>2288.84</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99">
+        <v>2278.3165816539672</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="1"/>
+        <v>2278.3200000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100">
+        <v>2201.534036992738</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="1"/>
+        <v>2201.5300000000002</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101">
+        <v>2129.6238599874559</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="1"/>
+        <v>2129.62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72729E67-0F39-48B1-BC56-FB08B4BA6520}">
   <dimension ref="A1:B101"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -446,7 +1676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -454,7 +1684,7 @@
         <v>2149.0100000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -462,7 +1692,7 @@
         <v>1958.52</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -470,7 +1700,7 @@
         <v>2194.31</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -478,7 +1708,7 @@
         <v>2456.91</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -486,7 +1716,7 @@
         <v>1929.75</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -494,7 +1724,7 @@
         <v>1929.76</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -502,7 +1732,7 @@
         <v>2473.7600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -510,7 +1740,7 @@
         <v>2230.23</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -518,7 +1748,7 @@
         <v>1859.16</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -526,7 +1756,7 @@
         <v>2162.77</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -534,7 +1764,7 @@
         <v>1860.97</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -542,7 +1772,7 @@
         <v>1860.28</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -550,7 +1780,7 @@
         <v>2072.59</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -558,7 +1788,7 @@
         <v>1426.02</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -566,7 +1796,7 @@
         <v>1482.52</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -574,7 +1804,7 @@
         <v>1831.31</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -582,7 +1812,7 @@
         <v>1696.15</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>2</v>
       </c>
@@ -590,7 +1820,7 @@
         <v>2094.27</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>2</v>
       </c>
@@ -598,7 +1828,7 @@
         <v>1727.59</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>2</v>
       </c>
@@ -606,7 +1836,7 @@
         <v>1576.31</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -614,7 +1844,7 @@
         <v>2439.69</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -622,7 +1852,7 @@
         <v>1932.27</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>2</v>
       </c>
@@ -630,7 +1860,7 @@
         <v>2020.26</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>2</v>
       </c>
@@ -638,7 +1868,7 @@
         <v>1572.58</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -646,7 +1876,7 @@
         <v>1836.69</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>2</v>
       </c>
@@ -654,7 +1884,7 @@
         <v>2033.28</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>2</v>
       </c>
@@ -662,7 +1892,7 @@
         <v>1654.7</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>2</v>
       </c>
@@ -670,7 +1900,7 @@
         <v>2112.71</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>2</v>
       </c>
@@ -678,7 +1908,7 @@
         <v>1819.81</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>2</v>
       </c>
@@ -686,7 +1916,7 @@
         <v>1912.49</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>2</v>
       </c>
@@ -694,7 +1924,7 @@
         <v>1819.49</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>2</v>
       </c>
@@ -702,7 +1932,7 @@
         <v>2555.6799999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>2</v>
       </c>
@@ -710,7 +1940,7 @@
         <v>1995.95</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>2</v>
       </c>
@@ -718,7 +1948,7 @@
         <v>1682.69</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>2</v>
       </c>
@@ -726,7 +1956,7 @@
         <v>2246.7600000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>2</v>
       </c>
@@ -734,7 +1964,7 @@
         <v>1633.75</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -742,7 +1972,7 @@
         <v>2062.66</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>2</v>
       </c>
@@ -750,7 +1980,7 @@
         <v>1412.1</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>2</v>
       </c>
@@ -758,7 +1988,7 @@
         <v>1601.54</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>2</v>
       </c>
@@ -766,7 +1996,7 @@
         <v>2059.06</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>2</v>
       </c>
@@ -774,7 +2004,7 @@
         <v>2221.54</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>2</v>
       </c>
@@ -782,7 +2012,7 @@
         <v>2051.41</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -790,7 +2020,7 @@
         <v>1965.31</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>2</v>
       </c>
@@ -798,7 +2028,7 @@
         <v>1909.67</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>2</v>
       </c>
@@ -806,7 +2036,7 @@
         <v>1556.44</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>2</v>
       </c>
@@ -814,7 +2044,7 @@
         <v>1784.05</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>2</v>
       </c>
@@ -822,7 +2052,7 @@
         <v>1861.81</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>2</v>
       </c>
@@ -830,7 +2060,7 @@
         <v>2317.14</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>2</v>
       </c>
@@ -838,7 +2068,7 @@
         <v>2103.09</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>2</v>
       </c>
@@ -846,7 +2076,7 @@
         <v>1471.09</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -854,7 +2084,7 @@
         <v>2297.23</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -862,7 +2092,7 @@
         <v>2084.48</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -870,7 +2100,7 @@
         <v>1996.92</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -878,7 +2108,7 @@
         <v>2383.5</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -886,7 +2116,7 @@
         <v>2509.3000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -894,7 +2124,7 @@
         <v>2479.38</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>3</v>
       </c>
@@ -902,7 +2132,7 @@
         <v>1948.23</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>3</v>
       </c>
@@ -910,7 +2140,7 @@
         <v>2107.2399999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>3</v>
       </c>
@@ -918,7 +2148,7 @@
         <v>2299.38</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -926,7 +2156,7 @@
         <v>2492.66</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>3</v>
       </c>
@@ -934,7 +2164,7 @@
         <v>2056.25</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>3</v>
       </c>
@@ -942,7 +2172,7 @@
         <v>2144.3000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>3</v>
       </c>
@@ -950,7 +2180,7 @@
         <v>1868.1</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>3</v>
       </c>
@@ -958,7 +2188,7 @@
         <v>1841.14</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>3</v>
       </c>
@@ -966,7 +2196,7 @@
         <v>2443.7600000000002</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -974,7 +2204,7 @@
         <v>2606.87</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>3</v>
       </c>
@@ -982,7 +2212,7 @@
         <v>2178.4</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>3</v>
       </c>
@@ -990,7 +2220,7 @@
         <v>2501.06</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>3</v>
       </c>
@@ -998,7 +2228,7 @@
         <v>2308.4899999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>3</v>
       </c>
@@ -1006,7 +2236,7 @@
         <v>2006.46</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>3</v>
       </c>
@@ -1014,7 +2244,7 @@
         <v>2308.42</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>3</v>
       </c>
@@ -1022,7 +2252,7 @@
         <v>2661.41</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -1030,7 +2260,7 @@
         <v>2189.25</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -1038,7 +2268,7 @@
         <v>2669.39</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>3</v>
       </c>
@@ -1046,7 +2276,7 @@
         <v>1414.08</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>3</v>
       </c>
@@ -1054,7 +2284,7 @@
         <v>2446.5700000000002</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +2292,7 @@
         <v>2226.11</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>3</v>
       </c>
@@ -1070,7 +2300,7 @@
         <v>2110.3000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>3</v>
       </c>
@@ -1078,7 +2308,7 @@
         <v>2227.5300000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>3</v>
       </c>
@@ -1086,7 +2316,7 @@
         <v>1603.73</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>3</v>
       </c>
@@ -1094,7 +2324,7 @@
         <v>2134.1</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>3</v>
       </c>
@@ -1102,7 +2332,7 @@
         <v>2307.13</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>3</v>
       </c>
@@ -1110,7 +2340,7 @@
         <v>2643.37</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>3</v>
       </c>
@@ -1118,7 +2348,7 @@
         <v>2044.52</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>3</v>
       </c>
@@ -1126,7 +2356,7 @@
         <v>1957.45</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>3</v>
       </c>
@@ -1134,7 +2364,7 @@
         <v>2049.4699999999998</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>3</v>
       </c>
@@ -1142,7 +2372,7 @@
         <v>2474.62</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>3</v>
       </c>
@@ -1150,7 +2380,7 @@
         <v>2298.63</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>3</v>
       </c>
@@ -1158,7 +2388,7 @@
         <v>2041.07</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>3</v>
       </c>
@@ -1166,7 +2396,7 @@
         <v>2353.98</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>3</v>
       </c>
@@ -1174,7 +2404,7 @@
         <v>2229.12</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>3</v>
       </c>
@@ -1182,7 +2412,7 @@
         <v>2490.59</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +2420,7 @@
         <v>1989.38</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>3</v>
       </c>
@@ -1198,7 +2428,7 @@
         <v>2101.6999999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>3</v>
       </c>
@@ -1206,7 +2436,7 @@
         <v>2082.37</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>3</v>
       </c>
@@ -1214,7 +2444,7 @@
         <v>1760.95</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>3</v>
       </c>
@@ -1222,7 +2452,7 @@
         <v>2288.84</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>3</v>
       </c>
@@ -1230,7 +2460,7 @@
         <v>2278.3200000000002</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>3</v>
       </c>
@@ -1238,11 +2468,437 @@
         <v>2201.5300000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>3</v>
       </c>
       <c r="B101">
+        <v>2129.62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52EFCEA6-CD66-4C97-B303-5079D7CF7AE6}">
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.1796875" customWidth="1"/>
+    <col min="7" max="7" width="43.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2149.0100000000002</v>
+      </c>
+      <c r="B2">
+        <v>2297.23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1958.52</v>
+      </c>
+      <c r="B3">
+        <v>2084.48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2194.31</v>
+      </c>
+      <c r="B4">
+        <v>1996.92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2456.91</v>
+      </c>
+      <c r="B5">
+        <v>2383.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1929.75</v>
+      </c>
+      <c r="B6">
+        <v>2509.3000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1929.76</v>
+      </c>
+      <c r="B7">
+        <v>2479.38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2473.7600000000002</v>
+      </c>
+      <c r="B8">
+        <v>1948.23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2230.23</v>
+      </c>
+      <c r="B9">
+        <v>2107.2399999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1859.16</v>
+      </c>
+      <c r="B10">
+        <v>2299.38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2162.77</v>
+      </c>
+      <c r="B11">
+        <v>2492.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1860.97</v>
+      </c>
+      <c r="B12">
+        <v>2056.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1860.28</v>
+      </c>
+      <c r="B13">
+        <v>2144.3000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2072.59</v>
+      </c>
+      <c r="B14">
+        <v>1868.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1426.02</v>
+      </c>
+      <c r="B15">
+        <v>1841.14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1482.52</v>
+      </c>
+      <c r="B16">
+        <v>2443.7600000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1831.31</v>
+      </c>
+      <c r="B17">
+        <v>2606.87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>1696.15</v>
+      </c>
+      <c r="B18">
+        <v>2178.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2094.27</v>
+      </c>
+      <c r="B19">
+        <v>2501.06</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1727.59</v>
+      </c>
+      <c r="B20">
+        <v>2308.4899999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1576.31</v>
+      </c>
+      <c r="B21">
+        <v>2006.46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2439.69</v>
+      </c>
+      <c r="B22">
+        <v>2308.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>1932.27</v>
+      </c>
+      <c r="B23">
+        <v>2661.41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2020.26</v>
+      </c>
+      <c r="B24">
+        <v>2189.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>1572.58</v>
+      </c>
+      <c r="B25">
+        <v>2669.39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>1836.69</v>
+      </c>
+      <c r="B26">
+        <v>1414.08</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>2033.28</v>
+      </c>
+      <c r="B27">
+        <v>2446.5700000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>1654.7</v>
+      </c>
+      <c r="B28">
+        <v>2226.11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2112.71</v>
+      </c>
+      <c r="B29">
+        <v>2110.3000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>1819.81</v>
+      </c>
+      <c r="B30">
+        <v>2227.5300000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>1912.49</v>
+      </c>
+      <c r="B31">
+        <v>1603.73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>1819.49</v>
+      </c>
+      <c r="B32">
+        <v>2134.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>2555.6799999999998</v>
+      </c>
+      <c r="B33">
+        <v>2307.13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>1995.95</v>
+      </c>
+      <c r="B34">
+        <v>2643.37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1682.69</v>
+      </c>
+      <c r="B35">
+        <v>2044.52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>2246.7600000000002</v>
+      </c>
+      <c r="B36">
+        <v>1957.45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>1633.75</v>
+      </c>
+      <c r="B37">
+        <v>2049.4699999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>2062.66</v>
+      </c>
+      <c r="B38">
+        <v>2474.62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>1412.1</v>
+      </c>
+      <c r="B39">
+        <v>2298.63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1601.54</v>
+      </c>
+      <c r="B40">
+        <v>2041.07</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>2059.06</v>
+      </c>
+      <c r="B41">
+        <v>2353.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>2221.54</v>
+      </c>
+      <c r="B42">
+        <v>2229.12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>2051.41</v>
+      </c>
+      <c r="B43">
+        <v>2490.59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1965.31</v>
+      </c>
+      <c r="B44">
+        <v>1989.38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1909.67</v>
+      </c>
+      <c r="B45">
+        <v>2101.6999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>1556.44</v>
+      </c>
+      <c r="B46">
+        <v>2082.37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>1784.05</v>
+      </c>
+      <c r="B47">
+        <v>1760.95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>1861.81</v>
+      </c>
+      <c r="B48">
+        <v>2288.84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>2317.14</v>
+      </c>
+      <c r="B49">
+        <v>2278.3200000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>2103.09</v>
+      </c>
+      <c r="B50">
+        <v>2201.5300000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1471.09</v>
+      </c>
+      <c r="B51">
         <v>2129.62</v>
       </c>
     </row>
@@ -1251,65 +2907,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{F7C9EE02-42E1-4005-9D12-6889AFFD525C}">
       <x15:webExtensions xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x15:webExtension appRef="{1A84D8ED-EDBE-4389-815D-03BCB1F0EAB6}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{AF05D9A6-3213-47C5-A090-5913DB7AD7C0}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{F8D5DCDE-76D2-4EDB-9A17-1ED74054BCA1}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{4E5163CD-4A01-4C2F-B75B-DFFE063C551E}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
         <x15:webExtension appRef="{226C29BB-503D-4118-82B0-797A5746FD0D}">
-          <xm:f>#REF!</xm:f>
+          <xm:f>solution!1:1048576</xm:f>
         </x15:webExtension>
         <x15:webExtension appRef="{4065FD8C-A093-4C11-91CA-652CDA52AB52}">
-          <xm:f>#REF!</xm:f>
+          <xm:f>solution!$A$1:$A$51</xm:f>
         </x15:webExtension>
         <x15:webExtension appRef="{A5D02EB9-33B0-429C-A955-773EB7B33603}">
-          <xm:f>#REF!</xm:f>
+          <xm:f>solution!$B$1:$B$51</xm:f>
         </x15:webExtension>
         <x15:webExtension appRef="{A08660AB-7F5E-4D56-87E9-DDC1447F4117}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{226C29BB-503D-4118-82B0-797A5746FD0D}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{4065FD8C-A093-4C11-91CA-652CDA52AB52}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{A5D02EB9-33B0-429C-A955-773EB7B33603}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{A08660AB-7F5E-4D56-87E9-DDC1447F4117}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{226C29BB-503D-4118-82B0-797A5746FD0D}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{4065FD8C-A093-4C11-91CA-652CDA52AB52}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{A5D02EB9-33B0-429C-A955-773EB7B33603}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{A08660AB-7F5E-4D56-87E9-DDC1447F4117}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{226C29BB-503D-4118-82B0-797A5746FD0D}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{4065FD8C-A093-4C11-91CA-652CDA52AB52}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{A5D02EB9-33B0-429C-A955-773EB7B33603}">
-          <xm:f>#REF!</xm:f>
-        </x15:webExtension>
-        <x15:webExtension appRef="{A08660AB-7F5E-4D56-87E9-DDC1447F4117}">
-          <xm:f>#REF!</xm:f>
+          <xm:f>solution!$D$16:$F$30</xm:f>
         </x15:webExtension>
       </x15:webExtensions>
     </ext>
@@ -1332,15 +2940,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DD084E42E705654B9CF1FB4D1B6F86C3" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="537e09eec9479df6b3b9277a829eeea6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb71b97d-9a65-4f5a-80e4-73af0d9029ad" xmlns:ns3="c7bf0040-ac83-4da7-b072-3c1b65a214b3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="954325e78edeaac226e03e3e0adada46" ns2:_="" ns3:_="">
     <xsd:import namespace="cb71b97d-9a65-4f5a-80e4-73af0d9029ad"/>
@@ -1604,14 +3203,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A726E7-A48D-4E05-91DC-6B9A65104EF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A726E7-A48D-4E05-91DC-6B9A65104EF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cb71b97d-9a65-4f5a-80e4-73af0d9029ad"/>
+    <ds:schemaRef ds:uri="c7bf0040-ac83-4da7-b072-3c1b65a214b3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA0FC64-5C45-4A9B-B8CB-A71AD4B7E2BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8CD3F01-88B2-487A-8514-F4005AFD80BE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cb71b97d-9a65-4f5a-80e4-73af0d9029ad"/>
+    <ds:schemaRef ds:uri="c7bf0040-ac83-4da7-b072-3c1b65a214b3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8CD3F01-88B2-487A-8514-F4005AFD80BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA0FC64-5C45-4A9B-B8CB-A71AD4B7E2BA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>